--- a/data/source/civics.xlsx
+++ b/data/source/civics.xlsx
@@ -610,17 +610,17 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Конституция Республики Узбекистан принята 8 декабря 1992 г.; в апреле 2023 г. по итогам всенародного референдума принята новая редакция Конституции с существенными изменениями (расширение перечня прав человека, изменение срока полномочий президента с 5 до 7 лет, ряд социальных гарантий). Государство устроено как унитарная президентская республика, в составе которой находится Республика Каракалпакстан, обладающая особым статусом (собственная конституция, не противоречащая общереспубликанской). Законодательную власть осуществляет двухпалатный парламент — Олий Мажлис, состоящий из Законодательной палаты (150 депутатов, избираются населением) и Сената (100 членов, часть избирается региональными представительными органами, часть назначается президентом). Исполнительную власть возглавляет Президент (глава государства, избираемый на всеобщих выборах) совместно с Кабинетом Министров во главе с премьер-министром. Судебную систему образуют Конституционный суд (рассматривает вопросы соответствия законов Конституции), Верховный суд (высшая инстанция по гражданским, уголовным и административным делам) и нижестоящие суды. Для целей повседневной жизни важно знать: официальным языком является узбекский, государственная символика — флаг, герб, гимн — закреплены Конституцией, а основные законы публикуются на официальном портале правовой информации lex.uz.</t>
+          <t>Конституция Республики Узбекистан принята 8 декабря 1992 г.; в апреле 2023 г. по итогам всенародного референдума принята новая редакция Конституции с существенными изменениями (расширение перечня прав человека, изменение срока полномочий президента с 5 до 7 лет, ряд социальных гарантий). Государство устроено как унитарная президентская республика, в составе которой находится Республика Каракалпакстан, обладающая особым статусом (собственная конституция, не противоречащая общереспубликанской). Законодательную власть осуществляет двухпалатный парламент — Олий Мажлис, состоящий из Законодательной палаты (150 депутатов, избираются населением) и Сената (65 членов, часть избирается региональными представительными органами, часть назначается президентом). Исполнительную власть возглавляет Президент (глава государства, избираемый на всеобщих выборах) совместно с Кабинетом Министров во главе с премьер-министром. Судебную систему образуют Конституционный суд (рассматривает вопросы соответствия законов Конституции), Верховный суд (высшая инстанция по гражданским, уголовным и административным делам) и нижестоящие суды. Для целей повседневной жизни важно знать: официальным языком является узбекский, государственная символика — флаг, герб, гимн — закреплены Конституцией, а основные законы публикуются на официальном портале правовой информации lex.uz.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>O‘zbekiston Respublikasi Konstitutsiyasi 1992-yil 8-dekabrda qabul qilingan; 2023-yil aprelida umumxalq referendumi natijalari bo‘yicha inson huquqlari ro‘yxatining kengaytirilishi, prezidentlik muddatining 5 yildan 7 yilga o‘zgartirilishi, bir qator ijtimoiy kafolatlarni o‘z ichiga olgan sezilarli o‘zgarishlar bilan Konstitutsiyaning yangi tahriri qabul qilindi. Davlat maxsus maqomga ega (umumrespublika Konstitutsiyasiga zid bo‘lmagan o‘z konstitutsiyasiga ega) Qoraqalpog‘iston Respublikasini o‘z tarkibiga olgan unitar prezidentlik respublikasi sifatida tuzilgan. Qonun chiqaruvchi hokimiyatni Qonunchilik palatasi (aholi tomonidan saylanadigan 150 deputat) va Senatdan (100 a’zo, bir qismi mintaqaviy vakillik organlari tomonidan saylanadi, bir qismi prezident tomonidan tayinlanadi) iborat ikki palatali parlament — Oliy Majlis amalga oshiradi. Ijro etuvchi hokimiyatga umumxalq saylovlarida saylanadigan davlat boshlig‘i — Prezident, Bosh vazir boshchiligidagi Vazirlar Mahkamasi bilan birga boshchilik qiladi. Sud tizimini Konstitutsiyaviy sud (qonunlarning Konstitutsiyaga muvofiqligi masalalarini ko‘rib chiqadi), Oliy sud (fuqarolik, jinoyat va ma’muriy ishlar bo‘yicha oliy instansiya) va quyi sudlar tashkil etadi. Kundalik hayot uchun quyidagilarni bilish muhim: rasmiy til o‘zbek tili, davlat ramzlari — bayroq, gerb, madhiya Konstitutsiyada mustahkamlangan, asosiy qonunlar rasmiy huquqiy axborot portali lex.uz da e’lon qilinadi.</t>
+          <t>O‘zbekiston Respublikasi Konstitutsiyasi 1992-yil 8-dekabrda qabul qilingan; 2023-yil aprelida umumxalq referendumi natijalari bo‘yicha inson huquqlari ro‘yxatining kengaytirilishi, prezidentlik muddatining 5 yildan 7 yilga o‘zgartirilishi, bir qator ijtimoiy kafolatlarni o‘z ichiga olgan sezilarli o‘zgarishlar bilan Konstitutsiyaning yangi tahriri qabul qilindi. Davlat maxsus maqomga ega (umumrespublika Konstitutsiyasiga zid bo‘lmagan o‘z konstitutsiyasiga ega) Qoraqalpog‘iston Respublikasini o‘z tarkibiga olgan unitar prezidentlik respublikasi sifatida tuzilgan. Qonun chiqaruvchi hokimiyatni Qonunchilik palatasi (aholi tomonidan saylanadigan 150 deputat) va Senatdan (65 a’zo, bir qismi mintaqaviy vakillik organlari tomonidan saylanadi, bir qismi prezident tomonidan tayinlanadi) iborat ikki palatali parlament — Oliy Majlis amalga oshiradi. Ijro etuvchi hokimiyatga umumxalq saylovlarida saylanadigan davlat boshlig‘i — Prezident, Bosh vazir boshchiligidagi Vazirlar Mahkamasi bilan birga boshchilik qiladi. Sud tizimini Konstitutsiyaviy sud (qonunlarning Konstitutsiyaga muvofiqligi masalalarini ko‘rib chiqadi), Oliy sud (fuqarolik, jinoyat va ma’muriy ishlar bo‘yicha oliy instansiya) va quyi sudlar tashkil etadi. Kundalik hayot uchun quyidagilarni bilish muhim: rasmiy til o‘zbek tili, davlat ramzlari — bayroq, gerb, madhiya Konstitutsiyada mustahkamlangan, asosiy qonunlar rasmiy huquqiy axborot portali lex.uz da e’lon qilinadi.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>The Constitution of the Republic of Uzbekistan was adopted on December 8, 1992; in April 2023, following a nationwide referendum, a new version of the Constitution was adopted with substantial changes (an expanded list of human rights, a change in the presidential term from 5 to 7 years, and a number of social guarantees). The state is structured as a unitary presidential republic that includes the Republic of Karakalpakstan, which has special status (its own constitution, not contradicting the republic-wide one). Legislative power is exercised by the bicameral Oliy Majlis, consisting of the Legislative Chamber (150 deputies elected by the population) and the Senate (100 members, some elected by regional representative bodies, some appointed by the president). Executive power is headed by the President (the head of state, elected in general elections) together with the Cabinet of Ministers led by the Prime Minister. The judicial system consists of the Constitutional Court (reviews the compliance of laws with the Constitution), the Supreme Court (the highest instance for civil, criminal and administrative cases), and lower courts. For everyday purposes it is useful to know: the official language is Uzbek; state symbols — the flag, coat of arms and anthem — are enshrined in the Constitution; and primary legislation is published on the official legal information portal lex.uz.</t>
+          <t>The Constitution of the Republic of Uzbekistan was adopted on December 8, 1992; in April 2023, following a nationwide referendum, a new version of the Constitution was adopted with substantial changes (an expanded list of human rights, a change in the presidential term from 5 to 7 years, and a number of social guarantees). The state is structured as a unitary presidential republic that includes the Republic of Karakalpakstan, which has special status (its own constitution, not contradicting the republic-wide one). Legislative power is exercised by the bicameral Oliy Majlis, consisting of the Legislative Chamber (150 deputies elected by the population) and the Senate (65 members, some elected by regional representative bodies, some appointed by the president). Executive power is headed by the President (the head of state, elected in general elections) together with the Cabinet of Ministers led by the Prime Minister. The judicial system consists of the Constitutional Court (reviews the compliance of laws with the Constitution), the Supreme Court (the highest instance for civil, criminal and administrative cases), and lower courts. For everyday purposes it is useful to know: the official language is Uzbek; state symbols — the flag, coat of arms and anthem — are enshrined in the Constitution; and primary legislation is published on the official legal information portal lex.uz.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Налоговый кодекс Республики Узбекистан устанавливает единую ставку налога на доходы физических лиц (НДФЛ) в размере 12% для налоговых резидентов (лиц, фактически находящихся в стране 183 дня и более в течение 12 месяцев). Для нерезидентов (в том числе иностранцев, чьё пребывание короче указанного срока) применяются иные ставки, которые периодически пересматриваются государством в целях привлечения инвестиций (например, льготная ставка на доходы нерезидентов от трудовой деятельности вводилась на уровне 12%, а по отдельным видам доходов, таким как дивиденды, проценты или доходы от фрахта, могут применяться повышенные ставки — актуальные цифры следует проверять в действующей редакции Налогового кодекса). Помимо НДФЛ, с заработной платы уплачиваются обязательные социальные взносы (в Пенсионный фонд и др.), которые в большинстве случаев удерживает и перечисляет работодатель, а работник получает «чистую» сумму на руки. Индивидуальные предприниматели и лица, занимающиеся частной практикой (в т.ч. иностранцы с соответствующим разрешением на трудовую деятельность), обязаны самостоятельно вести учёт доходов, подавать налоговую декларацию и уплачивать налоги в установленные сроки через персональный кабинет на портале Государственного налогового комитета (soliq.uz). Для иностранцев, приобретающих недвижимость или получающих доходы от источников в Узбекистане (аренда, продажа имущества), также могут возникать налоговые обязательства — рекомендуется заранее консультироваться с налоговым консультантом или в территориальном налоговом органе.</t>
+          <t>Налоговый кодекс Республики Узбекистан устанавливает единую ставку налога на доходы физических лиц (НДФЛ) в размере 12% для налоговых резидентов (лиц, фактически находящихся в стране 183 дня и более в течение 12 месяцев). Для нерезидентов (в том числе иностранцев, чьё пребывание короче указанного срока) применяются иные ставки, которые периодически пересматриваются государством в целях привлечения инвестиций (например, льготная ставка на доходы нерезидентов от трудовой деятельности вводилась на уровне 12%, а по отдельным видам доходов, таким как дивиденды, проценты или доходы от фрахта, могут применяться повышенные ставки — актуальные цифры следует проверять в действующей редакции Налогового кодекса). Помимо НДФЛ, с заработной платы уплачиваются обязательные социальные взносы (в Пенсионный фонд и др.), которые в большинстве случаев удерживает и перечисляет работодатель, а работник получает «чистую» сумму на руки. Индивидуальные предприниматели и лица, занимающиеся частной практикой (в т.ч. иностранцы с соответствующим разрешением на трудовую деятельность), обязаны самостоятельно вести учёт доходов, подавать налоговую декларацию и уплачивать налоги в установленные сроки через персональный кабинет на портале Налогового комитета (soliq.uz). Для иностранцев, приобретающих недвижимость или получающих доходы от источников в Узбекистане (аренда, продажа имущества), также могут возникать налоговые обязательства — рекомендуется заранее консультироваться с налоговым консультантом или в территориальном налоговом органе.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>O‘zbekiston Respublikasining Soliq kodeksi soliq rezidentlari (12 oy davomida mamlakatda haqiqatda 183 kun va undan ko‘proq bo‘lgan shaxslar) uchun jismoniy shaxslardan olinadigan daromad solig‘ining (JShDS) yagona 12% stavkasini belgilaydi. Norezidentlar (shu jumladan ko‘rsatilgan muddatdan qisqaroq bo‘lgan chet elliklar) uchun davlat tomonidan investitsiyalarni jalb qilish maqsadida davriy ravishda qayta ko‘rib chiqiladigan boshqa stavkalar qo‘llaniladi (masalan, norezidentlarning mehnat faoliyatidan olingan daromadlariga imtiyozli 12% stavka joriy etilgan, ayrim daromad turlari, masalan dividendlar, foizlar yoki frakt daromadlari bo‘yicha esa yuqori stavkalar qo‘llanishi mumkin — aniq raqamlarni Soliq kodeksining amaldagi tahririda tekshirish kerak). JShDSdan tashqari, ish haqidan majburiy ijtimoiy ajratmalar (Pensiya jamg‘armasiga va boshqalarga) to‘lanadi, ular ko‘pincha ish beruvchi tomonidan ushlab qolinadi va o‘tkaziladi, ishchi esa «sof» summani qo‘lga oladi. Yakka tartibdagi tadbirkorlar va xususiy amaliyot bilan shug‘ullanuvchi shaxslar (shu jumladan tegishli mehnat faoliyati ruxsatnomasiga ega chet elliklar) daromadlarini mustaqil hisobga olishi, soliq deklaratsiyasini topshirishi va belgilangan muddatlarda Davlat soliq qo‘mitasi portalidagi (soliq.uz) shaxsiy kabinet orqali soliqlarni to‘lashi shart. Ko‘chmas mulk sotib oluvchi yoki O‘zbekistondagi manbalardan daromad oluvchi (ijara, mulkni sotish) chet elliklar uchun ham soliq majburiyatlari yuzaga kelishi mumkin — oldindan soliq maslahatchisi yoki hududiy soliq organi bilan maslahatlashish tavsiya etiladi.</t>
+          <t>O‘zbekiston Respublikasining Soliq kodeksi soliq rezidentlari (12 oy davomida mamlakatda haqiqatda 183 kun va undan ko‘proq bo‘lgan shaxslar) uchun jismoniy shaxslardan olinadigan daromad solig‘ining (JShDS) yagona 12% stavkasini belgilaydi. Norezidentlar (shu jumladan ko‘rsatilgan muddatdan qisqaroq bo‘lgan chet elliklar) uchun davlat tomonidan investitsiyalarni jalb qilish maqsadida davriy ravishda qayta ko‘rib chiqiladigan boshqa stavkalar qo‘llaniladi (masalan, norezidentlarning mehnat faoliyatidan olingan daromadlariga imtiyozli 12% stavka joriy etilgan, ayrim daromad turlari, masalan dividendlar, foizlar yoki frakt daromadlari bo‘yicha esa yuqori stavkalar qo‘llanishi mumkin — aniq raqamlarni Soliq kodeksining amaldagi tahririda tekshirish kerak). JShDSdan tashqari, ish haqidan majburiy ijtimoiy ajratmalar (Pensiya jamg‘armasiga va boshqalarga) to‘lanadi, ular ko‘pincha ish beruvchi tomonidan ushlab qolinadi va o‘tkaziladi, ishchi esa «sof» summani qo‘lga oladi. Yakka tartibdagi tadbirkorlar va xususiy amaliyot bilan shug‘ullanuvchi shaxslar (shu jumladan tegishli mehnat faoliyati ruxsatnomasiga ega chet elliklar) daromadlarini mustaqil hisobga olishi, soliq deklaratsiyasini topshirishi va belgilangan muddatlarda Soliq qo‘mitasi portalidagi (soliq.uz) shaxsiy kabinet orqali soliqlarni to‘lashi shart. Ko‘chmas mulk sotib oluvchi yoki O‘zbekistondagi manbalardan daromad oluvchi (ijara, mulkni sotish) chet elliklar uchun ham soliq majburiyatlari yuzaga kelishi mumkin — oldindan soliq maslahatchisi yoki hududiy soliq organi bilan maslahatlashish tavsiya etiladi.</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>The Tax Code of the Republic of Uzbekistan sets a flat personal income tax (PIT) rate of 12% for tax residents (persons actually present in the country for 183 days or more within 12 months). For non-residents (including foreigners whose stay is shorter than that threshold), different rates apply, which the state periodically revises to attract investment (for example, a preferential rate on non-residents' labor income has been set at 12%, while certain income types such as dividends, interest, or freight income may be subject to higher rates — the exact figures should be checked against the current version of the Tax Code). In addition to PIT, mandatory social contributions (to the Pension Fund and others) are paid from wages, which in most cases are withheld and remitted by the employer, with the employee receiving the «net» amount. Individual entrepreneurs and persons engaged in private practice (including foreigners with an appropriate work permit) must independently keep records of income, file a tax return, and pay taxes by the set deadlines through a personal account on the State Tax Committee's portal (soliq.uz). Tax obligations may also arise for foreigners who purchase real estate or receive income from sources in Uzbekistan (rent, sale of property) — it is advisable to consult a tax advisor or the local tax office in advance.</t>
+          <t>The Tax Code of the Republic of Uzbekistan sets a flat personal income tax (PIT) rate of 12% for tax residents (persons actually present in the country for 183 days or more within 12 months). For non-residents (including foreigners whose stay is shorter than that threshold), different rates apply, which the state periodically revises to attract investment (for example, a preferential rate on non-residents' labor income has been set at 12%, while certain income types such as dividends, interest, or freight income may be subject to higher rates — the exact figures should be checked against the current version of the Tax Code). In addition to PIT, mandatory social contributions (to the Pension Fund and others) are paid from wages, which in most cases are withheld and remitted by the employer, with the employee receiving the «net» amount. Individual entrepreneurs and persons engaged in private practice (including foreigners with an appropriate work permit) must independently keep records of income, file a tax return, and pay taxes by the set deadlines through a personal account on the Tax Committee's portal (soliq.uz). Tax obligations may also arise for foreigners who purchase real estate or receive income from sources in Uzbekistan (rent, sale of property) — it is advisable to consult a tax advisor or the local tax office in advance.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Кодекс Республики Узбекистан об административной ответственности регулирует менее тяжкие нарушения, чем уголовные преступления. Типичные виды взысканий: предупреждение, штраф (исчисляется в базовых расчётных величинах — БРВ), административный арест (на короткий срок, за отдельные правонарушения), выдворение за пределы страны (для иностранцев — как дополнительная мера за грубые нарушения миграционного законодательства). Наиболее частые правонарушения, с которыми могут столкнуться иностранцы: нарушение сроков регистрации по месту пребывания (для иностранцев установлены короткие сроки постановки на учёт после въезда — как правило, несколько рабочих дней, точный срок нужно уточнять в момент въезда), нарушение визового режима (просроченная виза, работа без разрешения), нарушения правил дорожного движения (превышение скорости, вождение без прав или в состоянии опьянения — влечёт значительные штрафы и может повлечь лишение права управления), нарушение общественного порядка (мелкое хулиганство, распитие алкоголя в неположенных местах). Дела об административных правонарушениях рассматриваются уполномоченными органами (МВД, ГСБДД, миграционная служба) или судом (по более серьёзным составам, включая выдворение). У привлекаемого к ответственности лица есть право на защиту, ознакомление с материалами дела и обжалование решения в вышестоящий орган или суд в установленные сроки.</t>
+          <t>Кодекс Республики Узбекистан об административной ответственности регулирует менее тяжкие нарушения, чем уголовные преступления. Типичные виды взысканий: предупреждение, штраф (исчисляется в базовых расчётных величинах — БРВ), административный арест (на короткий срок, за отдельные правонарушения), выдворение за пределы страны (для иностранцев — как дополнительная мера за грубые нарушения миграционного законодательства). Наиболее частые правонарушения, с которыми могут столкнуться иностранцы: нарушение сроков регистрации по месту пребывания (для иностранцев установлены короткие сроки постановки на учёт после въезда — как правило, несколько рабочих дней, точный срок нужно уточнять в момент въезда), нарушение визового режима (просроченная виза, работа без разрешения), нарушения правил дорожного движения (превышение скорости, вождение без прав или в состоянии опьянения — влечёт значительные штрафы и может повлечь лишение права управления), нарушение общественного порядка (мелкое хулиганство, распитие алкоголя в неположенных местах). Дела об административных правонарушениях рассматриваются уполномоченными органами (МВД, служба безопасности дорожного движения, миграционная служба) или судом (по более серьёзным составам, включая выдворение). У привлекаемого к ответственности лица есть право на защиту, ознакомление с материалами дела и обжалование решения в вышестоящий орган или суд в установленные сроки.</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>O‘zbekiston Respublikasining Ma’muriy javobgarlik to‘g‘risidagi kodeksi jinoiy jinoyatlarga qaraganda kamroq og‘ir buzilishlarni tartibga soladi. Odatiy jazo turlari: ogohlantirish, jarima (bazaviy hisoblash miqdorlarida — BHM hisoblanadi), ma’muriy qamoqqa olish (qisqa muddatga, ayrim huquqbuzarliklar uchun), mamlakat hududidan chiqarib yuborish (chet elliklar uchun — migratsiya qonunchiligini qo‘pol buzganlik uchun qo‘shimcha chora sifatida). Chet elliklar duch kelishi mumkin bo‘lgan eng ko‘p uchraydigan huquqbuzarliklar: turgan joyida ro‘yxatdan o‘tish muddatlarini buzish (chet elliklar uchun kirgandan keyin hisobga qo‘yilish uchun qisqa muddatlar belgilangan — odatda bir necha ish kuni, aniq muddatni chegaradan kirish paytida aniqlashtirish kerak), viza tartibini buzish (muddati o‘tgan viza, ruxsatnomasiz ishlash), yo‘l harakati qoidalarini buzish (tezlikni oshirib yuborish, guvohnomasiz yoki mast holda haydash — sezilarli jarimalarga olib keladi va haydash huquqidan mahrum qilishga sabab bo‘lishi mumkin), jamoat tartibini buzish (mayda xuliganlik, ruxsat etilmagan joylarda spirtli ichimlik ichish). Ma’muriy huquqbuzarliklar to‘g‘risidagi ishlar vakolatli organlar (IIV, YHXBB, migratsiya xizmati) yoki sud (jiddiyroq tarkiblar, jumladan chiqarib yuborish bo‘yicha) tomonidan ko‘rib chiqiladi. Javobgarlikka tortilayotgan shaxs himoya qilish, ish materiallari bilan tanishish va belgilangan muddatlarda qarorni yuqori organga yoki sudga shikoyat qilish huquqiga ega.</t>
+          <t>O‘zbekiston Respublikasining Ma’muriy javobgarlik to‘g‘risidagi kodeksi jinoiy jinoyatlarga qaraganda kamroq og‘ir buzilishlarni tartibga soladi. Odatiy jazo turlari: ogohlantirish, jarima (bazaviy hisoblash miqdorlarida — BHM hisoblanadi), ma’muriy qamoqqa olish (qisqa muddatga, ayrim huquqbuzarliklar uchun), mamlakat hududidan chiqarib yuborish (chet elliklar uchun — migratsiya qonunchiligini qo‘pol buzganlik uchun qo‘shimcha chora sifatida). Chet elliklar duch kelishi mumkin bo‘lgan eng ko‘p uchraydigan huquqbuzarliklar: turgan joyida ro‘yxatdan o‘tish muddatlarini buzish (chet elliklar uchun kirgandan keyin hisobga qo‘yilish uchun qisqa muddatlar belgilangan — odatda bir necha ish kuni, aniq muddatni chegaradan kirish paytida aniqlashtirish kerak), viza tartibini buzish (muddati o‘tgan viza, ruxsatnomasiz ishlash), yo‘l harakati qoidalarini buzish (tezlikni oshirib yuborish, guvohnomasiz yoki mast holda haydash — sezilarli jarimalarga olib keladi va haydash huquqidan mahrum qilishga sabab bo‘lishi mumkin), jamoat tartibini buzish (mayda xuliganlik, ruxsat etilmagan joylarda spirtli ichimlik ichish). Ma’muriy huquqbuzarliklar to‘g‘risidagi ishlar vakolatli organlar (IIV, Yo‘l harakati xavfsizligi xizmati, migratsiya xizmati) yoki sud (jiddiyroq tarkiblar, jumladan chiqarib yuborish bo‘yicha) tomonidan ko‘rib chiqiladi. Javobgarlikka tortilayotgan shaxs himoya qilish, ish materiallari bilan tanishish va belgilangan muddatlarda qarorni yuqori organga yoki sudga shikoyat qilish huquqiga ega.</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -2230,17 +2230,17 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Трудоустройство иностранного гражданина в Узбекистане проходит через двухступенчатую разрешительную систему. Во-первых, работодатель (юридическое лицо или индивидуальный предприниматель) должен получить разрешение на привлечение иностранной рабочей силы — документ выдаётся Агентством по внешней трудовой миграции при Министерстве занятости и трудовых отношений и подтверждает право компании нанимать иностранцев в пределах установленной квоты (для ряда профессий и отраслей квоты не действуют или действуют льготные условия, например для IT-специалистов, преподавателей, высококвалифицированных менеджеров — правила периодически меняются). Во-вторых, для самого иностранного работника оформляется подтверждение на право осуществления трудовой деятельности на территории Узбекистана — этот документ выдаётся на конкретную должность у конкретного работодателя и не даёт права работать где-либо ещё без переоформления. В-третьих, иностранцу требуется рабочая виза (соответствующей категории), которая оформляется на основании указанных выше разрешительных документов. Только после получения всех трёх документов работодатель вправе заключить трудовой договор и допустить иностранца к работе; несоблюдение этого порядка влечёт административную ответственность как для работодателя (крупные штрафы, приостановление деятельности), так и для самого иностранного работника (штраф, возможное выдворение из страны). Существуют льготные или упрощённые режимы для отдельных категорий (граждане государств — членов ЕАЭС в части общих трудовых прав, высококвалифицированные специалисты в приоритетных отраслях, резиденты особых экономических/технологических зон), но конкретные условия следует уточнять непосредственно перед трудоустройством, так как перечень льгот периодически обновляется правительственными постановлениями.</t>
+          <t>Трудоустройство иностранного гражданина в Узбекистане проходит через двухступенчатую разрешительную систему. Во-первых, работодатель (юридическое лицо или индивидуальный предприниматель) должен получить разрешение на привлечение иностранной рабочей силы — документ выдаётся Агентством по внешней трудовой миграции при Министерстве занятости и сокращения бедности и подтверждает право компании нанимать иностранцев в пределах установленной квоты (для ряда профессий и отраслей квоты не действуют или действуют льготные условия, например для IT-специалистов, преподавателей, высококвалифицированных менеджеров — правила периодически меняются). Во-вторых, для самого иностранного работника оформляется подтверждение на право осуществления трудовой деятельности на территории Узбекистана — этот документ выдаётся на конкретную должность у конкретного работодателя и не даёт права работать где-либо ещё без переоформления. В-третьих, иностранцу требуется рабочая виза (соответствующей категории), которая оформляется на основании указанных выше разрешительных документов. Только после получения всех трёх документов работодатель вправе заключить трудовой договор и допустить иностранца к работе; несоблюдение этого порядка влечёт административную ответственность как для работодателя (крупные штрафы, приостановление деятельности), так и для самого иностранного работника (штраф, возможное выдворение из страны). Существуют льготные или упрощённые режимы для отдельных категорий (граждане государств — членов ЕАЭС в части общих трудовых прав, высококвалифицированные специалисты в приоритетных отраслях, резиденты особых экономических/технологических зон), но конкретные условия следует уточнять непосредственно перед трудоустройством, так как перечень льгот периодически обновляется правительственными постановлениями.</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>O‘zbekistonda chet ellik fuqaroni ishga joylashtirish ikki bosqichli ruxsat berish tizimi orqali amalga oshiriladi. Birinchidan, ish beruvchi (yuridik shaxs yoki yakka tartibdagi tadbirkor) chet ellik ishchi kuchini jalb qilish ruxsatnomasini olishi kerak — bu hujjat Bandlik va mehnat munosabatlari vazirligi huzuridagi Tashqi mehnat migratsiyasi agentligi tomonidan beriladi va kompaniyaning belgilangan kvota doirasida chet elliklarni yollash huquqini tasdiqlaydi (bir qator kasblar va sohalar uchun kvotalar amal qilmaydi yoki imtiyozli shartlar amal qiladi, masalan IT mutaxassislari, o‘qituvchilar, yuqori malakali menejerlar uchun — qoidalar davriy ravishda o‘zgarib turadi). Ikkinchidan, chet ellik ishchining o‘zi uchun O‘zbekiston hududida mehnat faoliyatini amalga oshirish huquqi to‘g‘risidagi tasdiqnoma rasmiylashtiriladi — bu hujjat aniq ish beruvchida aniq lavozim uchun beriladi va qayta rasmiylashtirmasdan boshqa joyda ishlash huquqini bermaydi. Uchinchidan, chet ellikka tegishli toifadagi ish vizasi kerak bo‘ladi, u yuqorida ko‘rsatilgan ruxsat beruvchi hujjatlar asosida rasmiylashtiriladi. Faqat barcha uchta hujjatni olganidan keyingina ish beruvchi mehnat shartnomasi tuzish va chet ellikni ishga qo‘yish huquqiga ega bo‘ladi; bu tartibga rioya qilmaslik ham ish beruvchi uchun (katta jarimalar, faoliyatni to‘xtatish), ham chet ellik ishchining o‘zi uchun (jarima, mamlakatdan chiqarib yuborilishi mumkinligi) ma’muriy javobgarlikka olib keladi. Ayrim toifalar uchun (umumiy mehnat huquqlari qismida YEIU a’zosi davlatlari fuqarolari, ustuvor sohalardagi yuqori malakali mutaxassislar, maxsus iqtisodiy/texnologik zonalar rezidentlari) imtiyozli yoki soddalashtirilgan tartiblar mavjud, biroq aniq shartlarni ishga joylashishdan bevosita oldin aniqlashtirish kerak, chunki imtiyozlar ro‘yxati hukumat qarorlari bilan davriy ravishda yangilanadi.</t>
+          <t>O‘zbekistonda chet ellik fuqaroni ishga joylashtirish ikki bosqichli ruxsat berish tizimi orqali amalga oshiriladi. Birinchidan, ish beruvchi (yuridik shaxs yoki yakka tartibdagi tadbirkor) chet ellik ishchi kuchini jalb qilish ruxsatnomasini olishi kerak — bu hujjat Bandlik va kambag‘allikni qisqartirish vazirligi huzuridagi Tashqi mehnat migratsiyasi agentligi tomonidan beriladi va kompaniyaning belgilangan kvota doirasida chet elliklarni yollash huquqini tasdiqlaydi (bir qator kasblar va sohalar uchun kvotalar amal qilmaydi yoki imtiyozli shartlar amal qiladi, masalan IT mutaxassislari, o‘qituvchilar, yuqori malakali menejerlar uchun — qoidalar davriy ravishda o‘zgarib turadi). Ikkinchidan, chet ellik ishchining o‘zi uchun O‘zbekiston hududida mehnat faoliyatini amalga oshirish huquqi to‘g‘risidagi tasdiqnoma rasmiylashtiriladi — bu hujjat aniq ish beruvchida aniq lavozim uchun beriladi va qayta rasmiylashtirmasdan boshqa joyda ishlash huquqini bermaydi. Uchinchidan, chet ellikka tegishli toifadagi ish vizasi kerak bo‘ladi, u yuqorida ko‘rsatilgan ruxsat beruvchi hujjatlar asosida rasmiylashtiriladi. Faqat barcha uchta hujjatni olganidan keyingina ish beruvchi mehnat shartnomasi tuzish va chet ellikni ishga qo‘yish huquqiga ega bo‘ladi; bu tartibga rioya qilmaslik ham ish beruvchi uchun (katta jarimalar, faoliyatni to‘xtatish), ham chet ellik ishchining o‘zi uchun (jarima, mamlakatdan chiqarib yuborilishi mumkinligi) ma’muriy javobgarlikka olib keladi. Ayrim toifalar uchun (umumiy mehnat huquqlari qismida YEIU a’zosi davlatlari fuqarolari, ustuvor sohalardagi yuqori malakali mutaxassislar, maxsus iqtisodiy/texnologik zonalar rezidentlari) imtiyozli yoki soddalashtirilgan tartiblar mavjud, biroq aniq shartlarni ishga joylashishdan bevosita oldin aniqlashtirish kerak, chunki imtiyozlar ro‘yxati hukumat qarorlari bilan davriy ravishda yangilanadi.</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Employment of a foreign citizen in Uzbekistan goes through a two-tier permit system. First, the employer (a legal entity or individual entrepreneur) must obtain a permit to attract foreign labor — this document is issued by the Agency for External Labor Migration under the Ministry of Employment and Labor Relations and confirms the company's right to hire foreigners within an established quota (for a number of professions and industries, quotas do not apply or preferential conditions apply, for example for IT specialists, teachers, and highly qualified managers — the rules change periodically). Second, for the foreign worker themselves, a confirmation of the right to carry out labor activity on the territory of Uzbekistan is issued — this document is granted for a specific position with a specific employer and does not give the right to work elsewhere without re-registration. Third, the foreigner needs a work visa of the appropriate category, issued on the basis of the permits described above. Only after obtaining all three documents is the employer entitled to conclude an employment contract and let the foreigner start work; failure to follow this procedure entails administrative liability both for the employer (substantial fines, suspension of activity) and for the foreign worker (a fine, possible expulsion from the country). There are preferential or simplified regimes for certain categories (citizens of EAEU member states with respect to general labor rights, highly qualified specialists in priority industries, residents of special economic/technology zones), but specific conditions should be checked directly before employment, as the list of benefits is periodically updated by government resolutions.</t>
+          <t>Employment of a foreign citizen in Uzbekistan goes through a two-tier permit system. First, the employer (a legal entity or individual entrepreneur) must obtain a permit to attract foreign labor — this document is issued by the Agency for External Labor Migration under the Ministry of Employment and Poverty Reduction and confirms the company's right to hire foreigners within an established quota (for a number of professions and industries, quotas do not apply or preferential conditions apply, for example for IT specialists, teachers, and highly qualified managers — the rules change periodically). Second, for the foreign worker themselves, a confirmation of the right to carry out labor activity on the territory of Uzbekistan is issued — this document is granted for a specific position with a specific employer and does not give the right to work elsewhere without re-registration. Third, the foreigner needs a work visa of the appropriate category, issued on the basis of the permits described above. Only after obtaining all three documents is the employer entitled to conclude an employment contract and let the foreigner start work; failure to follow this procedure entails administrative liability both for the employer (substantial fines, suspension of activity) and for the foreign worker (a fine, possible expulsion from the country). There are preferential or simplified regimes for certain categories (citizens of EAEU member states with respect to general labor rights, highly qualified specialists in priority industries, residents of special economic/technology zones), but specific conditions should be checked directly before employment, as the list of benefits is periodically updated by government resolutions.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Правила использования иностранных водительских удостоверений в Узбекистане зависят от участия страны происхождения в соответствующих международных конвенциях (например, Венской конвенции о дорожном движении): как правило, национальное водительское удостоверение вместе с международным водительским удостоверением (или его нотариально заверенным переводом) признаётся действительным для непродолжительного пребывания и вождения в стране; для длительного проживания (в частности, при получении ВНЖ) обычно требуется обменять иностранное удостоверение на национальное водительское удостоверение Узбекистана — порядок обмена, необходимость сдачи теоретического экзамена и перечень стран, с которыми предусмотрен упрощённый обмен, нужно уточнять в подразделении Государственной службы безопасности дорожного движения (ГСБДД/БДД). Основные правила дорожного движения в Узбекистане в целом схожи с общемировыми: правостороннее движение, обязательное использование ремней безопасности, ограничения скорости (обычно 60 км/ч в населённых пунктах, если не указано иное, и более высокие лимиты на трассах), запрет использования телефона за рулём без гарнитуры. Нарушения наказываются штрафами, начисляемыми в базовых расчётных величинах, а наиболее серьёзные — превышение скорости, вождение в состоянии алкогольного или наркотического опьянения, оставление места ДТП — влекут значительные штрафы, лишение права управления транспортным средством и в отдельных случаях уголовную ответственность (если причинён тяжкий вред здоровью или смерть). Иностранцу рекомендуется всегда иметь при себе оригиналы (или заверенные копии) водительского удостоверения, документов на автомобиль и полиса автогражданской ответственности (ОСАГО обязателен для владельцев транспортных средств).</t>
+          <t>Правила использования иностранных водительских удостоверений в Узбекистане зависят от участия страны происхождения в соответствующих международных конвенциях (например, Венской конвенции о дорожном движении): как правило, национальное водительское удостоверение вместе с международным водительским удостоверением (или его нотариально заверенным переводом) признаётся действительным для непродолжительного пребывания и вождения в стране; для длительного проживания (в частности, при получении ВНЖ) обычно требуется обменять иностранное удостоверение на национальное водительское удостоверение Узбекистана — порядок обмена, необходимость сдачи теоретического экзамена и перечень стран, с которыми предусмотрен упрощённый обмен, нужно уточнять в подразделении Службы безопасности дорожного движения Департамента общественной безопасности МВД. Основные правила дорожного движения в Узбекистане в целом схожи с общемировыми: правостороннее движение, обязательное использование ремней безопасности, ограничения скорости (обычно 60 км/ч в населённых пунктах, если не указано иное, и более высокие лимиты на трассах), запрет использования телефона за рулём без гарнитуры. Нарушения наказываются штрафами, начисляемыми в базовых расчётных величинах, а наиболее серьёзные — превышение скорости, вождение в состоянии алкогольного или наркотического опьянения, оставление места ДТП — влекут значительные штрафы, лишение права управления транспортным средством и в отдельных случаях уголовную ответственность (если причинён тяжкий вред здоровью или смерть). Иностранцу рекомендуется всегда иметь при себе оригиналы (или заверенные копии) водительского удостоверения, документов на автомобиль и полиса автогражданской ответственности (ОСАГО обязателен для владельцев транспортных средств).</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Chet ellik haydovchilik guvohnomalaridan O‘zbekistonda foydalanish qoidalari kelib chiqqan mamlakatning tegishli xalqaro konvensiyalarda (masalan, Yo‘l harakati to‘g‘risidagi Vena konvensiyasida) ishtirokiga bog‘liq: odatda milliy haydovchilik guvohnomasi xalqaro haydovchilik guvohnomasi (yoki uning notarial tasdiqlangan tarjimasi) bilan birga mamlakatda qisqa muddat bo‘lish va haydash uchun haqiqiy deb tan olinadi; uzoq muddat yashash uchun (xususan VNJ olishda) odatda chet ellik guvohnomani O‘zbekistonning milliy haydovchilik guvohnomasiga almashtirish talab qilinadi — almashtirish tartibi, nazariy imtihon topshirish zarurligi va soddalashtirilgan almashtirish nazarda tutilgan mamlakatlar ro‘yxatini Yo‘l harakati xavfsizligi davlat xizmati (YHXBB/BDD) bo‘limida aniqlashtirish kerak. O‘zbekistondagi asosiy yo‘l harakati qoidalari umuman olganda dunyo miqyosidagi qoidalarga o‘xshash: o‘ng tomonlama harakat, xavfsizlik kamarlaridan majburiy foydalanish, tezlik cheklovlari (agar boshqacha ko‘rsatilmagan bo‘lsa, aholi punktlarida odatda 60 km/soat, trassalarda yuqoriroq chegaralar), garnitursiz rulda telefondan foydalanishga taqiq. Buzilishlar bazaviy hisoblash miqdorlarida hisoblanadigan jarimalar bilan jazolanadi, eng jiddiylari — tezlikni oshirib yuborish, spirtli ichimlik yoki giyohvand moddalar ta’sirida haydash, YTH joyini tark etish — sezilarli jarimalar, transport vositasini boshqarish huquqidan mahrum qilish va ayrim hollarda (agar og‘ir sog‘liq zarari yoki o‘lim keltirib chiqarilgan bo‘lsa) jinoiy javobgarlikka olib keladi. Chet ellikka har doim haydovchilik guvohnomasining asl nusxasi (yoki tasdiqlangan nusxasi), avtomobil hujjatlari va fuqarolik javobgarligini sug‘urta qilish polisining (transport vositasi egalari uchun majburiy OSAGO) o‘zida bo‘lishi tavsiya etiladi.</t>
+          <t>Chet ellik haydovchilik guvohnomalaridan O‘zbekistonda foydalanish qoidalari kelib chiqqan mamlakatning tegishli xalqaro konvensiyalarda (masalan, Yo‘l harakati to‘g‘risidagi Vena konvensiyasida) ishtirokiga bog‘liq: odatda milliy haydovchilik guvohnomasi xalqaro haydovchilik guvohnomasi (yoki uning notarial tasdiqlangan tarjimasi) bilan birga mamlakatda qisqa muddat bo‘lish va haydash uchun haqiqiy deb tan olinadi; uzoq muddat yashash uchun (xususan VNJ olishda) odatda chet ellik guvohnomani O‘zbekistonning milliy haydovchilik guvohnomasiga almashtirish talab qilinadi — almashtirish tartibi, nazariy imtihon topshirish zarurligi va soddalashtirilgan almashtirish nazarda tutilgan mamlakatlar ro‘yxatini IIV Jamoat xavfsizligi departamentining Yo‘l harakati xavfsizligi xizmati bo‘limida aniqlashtirish kerak. O‘zbekistondagi asosiy yo‘l harakati qoidalari umuman olganda dunyo miqyosidagi qoidalarga o‘xshash: o‘ng tomonlama harakat, xavfsizlik kamarlaridan majburiy foydalanish, tezlik cheklovlari (agar boshqacha ko‘rsatilmagan bo‘lsa, aholi punktlarida odatda 60 km/soat, trassalarda yuqoriroq chegaralar), garnitursiz rulda telefondan foydalanishga taqiq. Buzilishlar bazaviy hisoblash miqdorlarida hisoblanadigan jarimalar bilan jazolanadi, eng jiddiylari — tezlikni oshirib yuborish, spirtli ichimlik yoki giyohvand moddalar ta’sirida haydash, YTH joyini tark etish — sezilarli jarimalar, transport vositasini boshqarish huquqidan mahrum qilish va ayrim hollarda (agar og‘ir sog‘liq zarari yoki o‘lim keltirib chiqarilgan bo‘lsa) jinoiy javobgarlikka olib keladi. Chet ellikka har doim haydovchilik guvohnomasining asl nusxasi (yoki tasdiqlangan nusxasi), avtomobil hujjatlari va fuqarolik javobgarligini sug‘urta qilish polisining (transport vositasi egalari uchun majburiy OSAGO) o‘zida bo‘lishi tavsiya etiladi.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Rules for using foreign driving licenses in Uzbekistan depend on whether the country of origin participates in the relevant international conventions (for example, the Vienna Convention on Road Traffic): as a rule, a national driving license together with an international driving permit (or its notarized translation) is recognized as valid for a short stay and driving in the country; for long-term residence (in particular, when obtaining a residence permit), it is usually necessary to exchange the foreign license for a national Uzbek driving license — the exchange procedure, whether a theory test is required, and the list of countries with a simplified exchange should be checked at the State Road Traffic Safety Service (traffic police). The basic traffic rules in Uzbekistan are broadly similar to worldwide standards: right-hand traffic, mandatory seatbelt use, speed limits (usually 60 km/h in populated areas unless otherwise indicated, and higher limits on highways), and a ban on using a phone while driving without a hands-free kit. Violations are punished with fines calculated in base calculation units, with the most serious ones — speeding, driving under the influence of alcohol or drugs, and leaving the scene of an accident — leading to substantial fines, loss of driving privileges, and in some cases criminal liability (if serious harm to health or death results). A foreigner is advised to always carry the original (or a certified copy) of their driving license, vehicle documents, and a third-party liability insurance policy (mandatory OSAGO insurance for vehicle owners).</t>
+          <t>Rules for using foreign driving licenses in Uzbekistan depend on whether the country of origin participates in the relevant international conventions (for example, the Vienna Convention on Road Traffic): as a rule, a national driving license together with an international driving permit (or its notarized translation) is recognized as valid for a short stay and driving in the country; for long-term residence (in particular, when obtaining a residence permit), it is usually necessary to exchange the foreign license for a national Uzbek driving license — the exchange procedure, whether a theory test is required, and the list of countries with a simplified exchange should be checked at the Road Traffic Safety Service of the Ministry of Internal Affairs (traffic police). The basic traffic rules in Uzbekistan are broadly similar to worldwide standards: right-hand traffic, mandatory seatbelt use, speed limits (usually 60 km/h in populated areas unless otherwise indicated, and higher limits on highways), and a ban on using a phone while driving without a hands-free kit. Violations are punished with fines calculated in base calculation units, with the most serious ones — speeding, driving under the influence of alcohol or drugs, and leaving the scene of an accident — leading to substantial fines, loss of driving privileges, and in some cases criminal liability (if serious harm to health or death results). A foreigner is advised to always carry the original (or a certified copy) of their driving license, vehicle documents, and a third-party liability insurance policy (mandatory OSAGO insurance for vehicle owners).</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Государственный налоговый комитет (декларации, ИНН)</t>
+          <t>Налоговый комитет (декларации, ИНН)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Davlat soliq qo‘mitasi (deklaratsiyalar, STIR)</t>
+          <t>Soliq qo‘mitasi (deklaratsiyalar, STIR)</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>State Tax Committee (tax returns, TIN)</t>
+          <t>Tax Committee (tax returns, TIN)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
